--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24829EDD-EABC-4B55-9588-12C731206A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8938C7-0D7F-46B6-A075-C6728B629197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="105">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -43,12 +43,6 @@
     <t>REBAIXA - MERCEARIA</t>
   </si>
   <si>
-    <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
-  </si>
-  <si>
-    <t>AMENDOIM SINHA 400G BRANCO</t>
-  </si>
-  <si>
     <t>#01 MERCEARIA - #02 ÓLEOS E GORDURAS</t>
   </si>
   <si>
@@ -73,6 +67,12 @@
     <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
   </si>
   <si>
+    <t>BISCOITO VITARELLA 350G AGUA TRADICIONAL</t>
+  </si>
+  <si>
+    <t>BISCOITO WAFER VIVALE 80G CHOCOLATE</t>
+  </si>
+  <si>
     <t>TORTILHA SNACKLINE 100G CHEESE WAFER CLASSIC</t>
   </si>
   <si>
@@ -151,10 +151,16 @@
     <t>ARROZINA MAIZENA 180G TRADICIONAL</t>
   </si>
   <si>
+    <t>CREMOGEMA 180G CHOCOLATE</t>
+  </si>
+  <si>
     <t>REBAIXA - CREMOGEMA</t>
   </si>
   <si>
-    <t>CREMOGEMA MORANGO 180G</t>
+    <t>CREMOGEMA 180G MORANGO</t>
+  </si>
+  <si>
+    <t>FARINHA DE TRIGO SABORELLE 1KG SEM FERMENTO</t>
   </si>
   <si>
     <t>FAROFA ARTESANAL KODILAR EDU GUEDES 250G</t>
@@ -164,6 +170,12 @@
   </si>
   <si>
     <t>MISTURA PARA BOLOS ITALAC 400G INTEGRAL BANANA</t>
+  </si>
+  <si>
+    <t>MUCILON NESTLÉ LATA 400G ARROZ AVEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUCILON NESTLÉ SACHÊ 600G MULTICEREAIS </t>
   </si>
   <si>
     <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
@@ -332,7 +344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,26 +380,8 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,12 +392,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45A045"/>
-        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -451,22 +439,10 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -775,15 +751,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -802,7 +778,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -814,31 +790,31 @@
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>178942</v>
+        <v>100059</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="10">
-        <v>7.99</v>
+      <c r="F2" s="7">
+        <v>13.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>100055</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7">
-        <v>100059</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11">
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
         <v>13.99</v>
       </c>
     </row>
@@ -847,35 +823,35 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
-        <v>100055</v>
+        <v>186551</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="10">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="F4" s="7">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
-        <v>186551</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C6" s="3">
+        <v>316642</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="10">
-        <v>45.99</v>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -886,14 +862,14 @@
         <v>14</v>
       </c>
       <c r="C7" s="3">
-        <v>316642</v>
+        <v>266385</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="10">
-        <v>16.989999999999998</v>
+      <c r="F7" s="7">
+        <v>6.19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,17 +877,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3">
+        <v>269692</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
-        <v>293173</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="10">
-        <v>17.989999999999998</v>
+      <c r="F8" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -919,17 +895,17 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
-        <v>173683</v>
+        <v>293173</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="10">
-        <v>19.989999999999998</v>
+      <c r="F9" s="7">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,14 +916,14 @@
         <v>18</v>
       </c>
       <c r="C10" s="3">
-        <v>185461</v>
+        <v>173683</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="10">
-        <v>10.99</v>
+      <c r="F10" s="7">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -955,17 +931,17 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
-        <v>100912</v>
+        <v>185461</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="10">
-        <v>1.99</v>
+      <c r="F11" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -976,14 +952,14 @@
         <v>21</v>
       </c>
       <c r="C12" s="3">
-        <v>276646</v>
+        <v>100912</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="10">
-        <v>16.989999999999998</v>
+      <c r="F12" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -994,32 +970,32 @@
         <v>21</v>
       </c>
       <c r="C13" s="3">
-        <v>276647</v>
+        <v>276646</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="10">
-        <v>15.99</v>
+      <c r="F13" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="3">
-        <v>279281</v>
+        <v>276647</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="10">
-        <v>2.69</v>
+      <c r="F14" s="7">
+        <v>15.99</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1030,34 +1006,32 @@
         <v>21</v>
       </c>
       <c r="C15" s="3">
-        <v>133147</v>
+        <v>279281</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="10">
-        <v>4.1900000000000004</v>
+      <c r="F15" s="7">
+        <v>2.69</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="3">
-        <v>307031</v>
+        <v>133147</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="10">
-        <v>4.49</v>
+        <v>27</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1068,14 +1042,16 @@
         <v>21</v>
       </c>
       <c r="C17" s="3">
-        <v>307025</v>
+        <v>307031</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="10">
-        <v>7.99</v>
+        <v>28</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="7">
+        <v>4.49</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1086,14 +1062,14 @@
         <v>21</v>
       </c>
       <c r="C18" s="3">
-        <v>307036</v>
+        <v>307025</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="10">
-        <v>6.99</v>
+      <c r="F18" s="7">
+        <v>7.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1104,14 +1080,14 @@
         <v>21</v>
       </c>
       <c r="C19" s="3">
-        <v>276643</v>
+        <v>307036</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="10">
-        <v>14.99</v>
+      <c r="F19" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1122,14 +1098,14 @@
         <v>21</v>
       </c>
       <c r="C20" s="3">
-        <v>312979</v>
+        <v>276643</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="10">
-        <v>16.989999999999998</v>
+      <c r="F20" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1140,68 +1116,68 @@
         <v>21</v>
       </c>
       <c r="C21" s="3">
+        <v>312979</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="3">
         <v>260235</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="10">
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
         <v>8.49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C23" s="3">
         <v>312226</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="11">
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
         <v>20.99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="7">
-        <v>253733</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="11">
-        <v>11.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C24" s="3">
-        <v>267751</v>
+        <v>253733</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="10">
-        <v>4.99</v>
+      <c r="F24" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,34 +1185,34 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3">
-        <v>225677</v>
+        <v>267751</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <v>4.99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="3">
-        <v>227346</v>
+        <v>225677</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="10">
+      <c r="F26" s="7">
         <v>4.99</v>
       </c>
     </row>
@@ -1248,34 +1224,32 @@
         <v>41</v>
       </c>
       <c r="C27" s="3">
-        <v>329064</v>
+        <v>226952</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3">
+        <v>227346</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="10">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="7">
-        <v>314154</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="11">
-        <v>6.49</v>
+      <c r="E28" s="5"/>
+      <c r="F28" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1283,167 +1257,167 @@
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3">
-        <v>243305</v>
+        <v>100029</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="10">
-        <v>18.989999999999998</v>
+      <c r="F29" s="7">
+        <v>6.59</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3">
-        <v>226255</v>
+        <v>329064</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="10">
-        <v>19.989999999999998</v>
+        <v>48</v>
+      </c>
+      <c r="F30" s="7">
+        <v>5.99</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="7">
-        <v>229268</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="11">
-        <v>11.99</v>
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="3">
+        <v>314154</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="7">
+        <v>6.49</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="3">
+        <v>101541</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="3">
+        <v>172735</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="3">
-        <v>334462</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="10">
-        <v>10.39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="7">
-        <v>113525</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="11">
-        <v>11.99</v>
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="7">
-        <v>312242</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="11">
-        <v>9.99</v>
+      <c r="A34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="3">
+        <v>243305</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="3">
+        <v>226255</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="7">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3">
+        <v>229268</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="3">
-        <v>150940</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="10">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="7">
-        <v>329822</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="11">
-        <v>17.989999999999998</v>
+      <c r="E36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="7">
-        <v>312228</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="11">
-        <v>9.99</v>
+      <c r="A37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="3">
+        <v>334462</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="7">
+        <v>10.39</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1451,17 +1425,19 @@
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C38" s="3">
-        <v>330718</v>
+        <v>113525</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="10">
-        <v>23.99</v>
+        <v>63</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1469,368 +1445,458 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C39" s="3">
-        <v>312232</v>
+        <v>312242</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="3">
+        <v>150940</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="10">
+      <c r="E40" s="5"/>
+      <c r="F40" s="7">
         <v>9.99</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="3">
+        <v>329822</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="E41" s="5"/>
+      <c r="F41" s="7">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="3">
+        <v>312228</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="3">
-        <v>297195</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="10">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="7">
-        <v>149057</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="11">
-        <v>18.989999999999998</v>
+      <c r="E42" s="5"/>
+      <c r="F42" s="7">
+        <v>9.99</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C43" s="3">
-        <v>297199</v>
+        <v>330718</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="10">
-        <v>13.99</v>
+      <c r="F43" s="7">
+        <v>23.99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C44" s="3">
-        <v>223067</v>
+        <v>312232</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="10">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="3">
-        <v>208304</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="10">
-        <v>6.99</v>
+      <c r="F44" s="7">
+        <v>9.99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="3">
+        <v>297195</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="3">
-        <v>236344</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="10">
-        <v>7.99</v>
+      <c r="F46" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C47" s="3">
-        <v>301257</v>
+        <v>149057</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="10">
-        <v>4.99</v>
+      <c r="F47" s="7">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C48" s="3">
-        <v>258212</v>
+        <v>297199</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="10">
-        <v>26.99</v>
+      <c r="F48" s="7">
+        <v>13.99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C49" s="3">
-        <v>258194</v>
+        <v>223067</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" s="10">
-        <v>28.99</v>
+      <c r="F49" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="3">
+        <v>208304</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="3">
-        <v>287446</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="10">
-        <v>24.99</v>
+      <c r="F50" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C51" s="3">
-        <v>292475</v>
+        <v>236344</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="10">
-        <v>32.99</v>
+      <c r="F51" s="7">
+        <v>7.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="7">
-        <v>219359</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="11">
+      <c r="A52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="3">
+        <v>301257</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="7">
         <v>4.99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C53" s="3">
-        <v>294469</v>
+        <v>258212</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E53" s="5"/>
-      <c r="F53" s="10">
-        <v>9.99</v>
+      <c r="F53" s="7">
+        <v>26.99</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C54" s="3">
-        <v>181531</v>
+        <v>258194</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E54" s="5"/>
-      <c r="F54" s="10">
-        <v>29.99</v>
+      <c r="F54" s="7">
+        <v>28.99</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="3">
+        <v>287446</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="7">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="3">
+        <v>292475</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="3">
-        <v>288809</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="10">
-        <v>23.99</v>
+      <c r="E56" s="5"/>
+      <c r="F56" s="7">
+        <v>32.99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C57" s="3">
-        <v>330232</v>
+        <v>219359</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F57" s="10">
-        <v>11.99</v>
+        <v>89</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="3">
+        <v>294469</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="3">
+        <v>181531</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="7">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="3">
+        <v>288809</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="7">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C62" s="3">
+        <v>330232</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="7">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="3">
         <v>294506</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="10">
+      <c r="D63" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" s="7">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="3">
         <v>168916</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="11">
+      <c r="D65" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="7">
         <v>3.49</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" s="7">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="3">
         <v>180239</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="11">
+      <c r="D66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="7">
         <v>3.49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C838F11-9675-4603-9972-82986BB54E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6A54C0-8CAB-4C5B-9F42-50F2590107FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="148">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -217,15 +217,9 @@
     <t>MANTEIGA AVIAÇÃO POTE 200G SEM SAL</t>
   </si>
   <si>
-    <t>REBAIXA VAQUINHA</t>
-  </si>
-  <si>
     <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
   </si>
   <si>
-    <t>IOGURTE DA VAQUINHA PIT 100G COCO</t>
-  </si>
-  <si>
     <t>TODDYNHO 200ML CHOCOLATE</t>
   </si>
   <si>
@@ -298,6 +292,27 @@
     <t>ALECRIM E GENGIBRE, BABOSA E BIOTINA</t>
   </si>
   <si>
+    <t>REBAIXA - COSMETICOS SNOOP ATÉ 30/04/26</t>
+  </si>
+  <si>
+    <t>CONDICIONADOR INFANTIL COTTONBABY SNOOPY 200ML</t>
+  </si>
+  <si>
+    <t>ALGODÃO, CAMOMILA</t>
+  </si>
+  <si>
+    <t>HIDRATANTE INFANTIL COTTONBABY SNOOPY 200ML</t>
+  </si>
+  <si>
+    <t>HORA DE NINAR, MELANINA</t>
+  </si>
+  <si>
+    <t>REBAIXA - HIDRATANTE ORIGEM ATÉ 04/2026</t>
+  </si>
+  <si>
+    <t>HIDRATANTE NAZCA 380ML ORIGEM MACADAMIA</t>
+  </si>
+  <si>
     <t>KIT SHAMPOO E CONDICIONADOR COTTONBABY SNOOPY INFANTIL</t>
   </si>
   <si>
@@ -307,6 +322,9 @@
     <t>SHAMPOO GOTA DOURADA 300ML OLEO DE COCO E RICINO</t>
   </si>
   <si>
+    <t>SHAMPOO INFANTIL COTTONBABY SNOOPY 200ML</t>
+  </si>
+  <si>
     <t>ÓLEO CAPILAR ALQUIMIA 120ML MAMONA</t>
   </si>
   <si>
@@ -316,6 +334,15 @@
     <t xml:space="preserve">DESODORANTE AERO 150ML GIOVANNA BABY BLUEBERRY </t>
   </si>
   <si>
+    <t>REBAIXA - DESODORANTE MOOD ATE 31/05/26</t>
+  </si>
+  <si>
+    <t>DESODORANTE MOOD AEROSOL 150ML</t>
+  </si>
+  <si>
+    <t>ENERGY MEN, FEMININO FLOR LAVANDA, FEMININO HIDRATANTE, FEMININO HIDRATANTE PROTECT, FEMININO HIDRATAÇÃO INTENSA, FLOR DE ALGODAO WOMEN, FRUTAS VERMELHA, IMPACT MEN, INVISIBLE CARE, MEN, MEN SPORT, POWER MEN, PROTECT UNISSEX, SEM PERFUME, TEEN BOY, TEEN GIRL, UNISSEX SPORT, WOMEN, WOMEN SPORT</t>
+  </si>
+  <si>
     <t>DESODORANTE MOOD AEROSOL 150ML PROTECT UNISSEX</t>
   </si>
   <si>
@@ -328,6 +355,9 @@
     <t>ESMALTE COLORAMA 8ML</t>
   </si>
   <si>
+    <t>AVISA QUE E FINI, CREMOSO VERDE NÃO DIVIDO MINHA FINI, FINI ME PATROCINA, FOI AQUI PEDIRAM FINI, FOI AQUI QUE PEDIRA, NÃO DIVIDO MINHA FINI, TA CHOVENDO</t>
+  </si>
+  <si>
     <t>#04 HIGIENE PESSOAL - FRALDAS</t>
   </si>
   <si>
@@ -358,12 +388,24 @@
     <t>#04 HIGIENE PESSOAL - INTIMA</t>
   </si>
   <si>
+    <t>AGUA MICELAR DERMATTIVE 150ML BIFASICA</t>
+  </si>
+  <si>
     <t>CERA DEPILATORIA PELO E PELE 350G MARACUJÁ</t>
   </si>
   <si>
+    <t>CREME PELO&amp;PELE 120GR CRAVOS E ESPINHAS</t>
+  </si>
+  <si>
     <t>ESFOLIANTE DOKMOS 160G GELEIA DE AMORA</t>
   </si>
   <si>
+    <t>HIDRATANTE CORPORAL NAZCA ORIGEM 380ML</t>
+  </si>
+  <si>
+    <t>BAUNILHA, CEREJA AVELÃ, COCO, ERVA DOCE, LAVANDA</t>
+  </si>
+  <si>
     <t>HIDRATANTE PELO&amp;PELE 280G KIT AXILA E VIRILHA</t>
   </si>
   <si>
@@ -379,6 +421,15 @@
     <t>#04 HIGIENE PESSOAL - SABONETE</t>
   </si>
   <si>
+    <t>SABONETE COTTONBABY SNOOPY BABY 200ML HORA DE NINAR</t>
+  </si>
+  <si>
+    <t>SABONETE HYDRATTA 85G CASTANHA</t>
+  </si>
+  <si>
+    <t>SABONETE LIQUIDO INFANTIL COTTONBABY SNOOPY 200ML ALGODÃO</t>
+  </si>
+  <si>
     <t>SABONETE LIQUIDO INTIMO INTIMUS FRESH 200ML</t>
   </si>
   <si>
@@ -386,6 +437,15 @@
   </si>
   <si>
     <t>SABONETE LIQUIDO TURMA DA XUXINHIA INFANTIL 400ML</t>
+  </si>
+  <si>
+    <t>#04 HIGIENE PESSOAL - TALCOS</t>
+  </si>
+  <si>
+    <t>TALCO INFANTIL COTTONBABY 90G SNOOPY CREMOSO</t>
+  </si>
+  <si>
+    <t>TALCO TABU 100G DESODORANTE PERFUMADO</t>
   </si>
   <si>
     <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
@@ -413,7 +473,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,34 +509,8 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,12 +521,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -523,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -547,21 +575,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -864,17 +877,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F95"/>
+  <sheetFormatPr defaultColWidth="31" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1081,20 +1088,20 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="3">
         <v>334706</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
         <v>12.99</v>
       </c>
     </row>
@@ -1117,38 +1124,38 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="3">
         <v>237036</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13">
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
         <v>13.99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="3">
         <v>173683</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13">
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -1231,20 +1238,20 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="3">
         <v>200247</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13">
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
@@ -1321,58 +1328,58 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="3">
         <v>307031</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="7">
         <v>4.49</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="3">
         <v>307025</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13">
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
         <v>7.99</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="3">
         <v>307036</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13">
+      <c r="E28" s="5"/>
+      <c r="F28" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -1485,40 +1492,40 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="3">
         <v>100029</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="13">
+      <c r="E35" s="5"/>
+      <c r="F35" s="7">
         <v>6.59</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="3">
         <v>329064</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="7">
         <v>5.99</v>
       </c>
     </row>
@@ -1597,39 +1604,39 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="9" t="s">
+      <c r="A41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="3">
         <v>243305</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="12"/>
-      <c r="F41" s="13">
+      <c r="E41" s="5"/>
+      <c r="F41" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="3">
+        <v>101874</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C42" s="3">
-        <v>107829</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="7">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1637,17 +1644,17 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="3">
-        <v>101874</v>
+        <v>307583</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>68</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="7">
-        <v>2.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1658,7 +1665,7 @@
         <v>69</v>
       </c>
       <c r="C44" s="3">
-        <v>307583</v>
+        <v>308401</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>70</v>
@@ -1673,15 +1680,17 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="3">
+        <v>308398</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="3">
-        <v>308401</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="5"/>
       <c r="F45" s="7">
         <v>12.99</v>
       </c>
@@ -1691,644 +1700,866 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C46" s="3">
-        <v>308398</v>
+        <v>308395</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="E46" s="5"/>
       <c r="F46" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="3">
-        <v>308395</v>
-      </c>
-      <c r="D47" s="4" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
-        <v>12.99</v>
+      <c r="C48" s="3">
+        <v>317113</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3">
-        <v>317113</v>
+        <v>240883</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F49" s="7">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C50" s="3">
-        <v>240883</v>
+        <v>311763</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E50" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="E50" s="5"/>
       <c r="F50" s="7">
-        <v>8.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="10">
-        <v>311763</v>
-      </c>
-      <c r="D51" s="11" t="s">
+      <c r="C51" s="3">
+        <v>100454</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="13">
+      <c r="E51" s="5"/>
+      <c r="F51" s="7">
         <v>10.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C52" s="3">
-        <v>100454</v>
+        <v>305348</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="7">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="2" t="s">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="3">
-        <v>305348</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="C54" s="3">
+        <v>305478</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
-        <v>20.99</v>
+      <c r="E54" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="10">
-        <v>305478</v>
-      </c>
-      <c r="D55" s="11" t="s">
+      <c r="A55" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="B55" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="3">
+        <v>281861</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F55" s="13">
+      <c r="E55" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" s="7">
         <v>11.99</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C56" s="3">
-        <v>316152</v>
+        <v>316151</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E56" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="F56" s="7">
-        <v>26.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C57" s="3">
-        <v>149057</v>
+        <v>266074</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="7">
-        <v>18.989999999999998</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="3">
-        <v>297199</v>
+        <v>316152</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="7">
-        <v>13.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C59" s="3">
-        <v>223067</v>
+        <v>149057</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="7">
-        <v>16.989999999999998</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="10">
-        <v>219798</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="13">
-        <v>12.99</v>
+      <c r="A60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="3">
+        <v>297199</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="7">
+        <v>13.99</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C61" s="3">
-        <v>208304</v>
+        <v>281785</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="F61" s="7">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C62" s="3">
-        <v>236344</v>
+        <v>223067</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="7">
-        <v>7.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C63" s="3">
-        <v>301257</v>
+        <v>219798</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="7">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C64" s="3">
-        <v>272192</v>
+        <v>208281</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="F64" s="7">
-        <v>32.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C65" s="3">
-        <v>298620</v>
+        <v>208304</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="7">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="3">
-        <v>258194</v>
+        <v>236344</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="7">
-        <v>28.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C67" s="3">
-        <v>258212</v>
+        <v>301257</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E67" s="5"/>
+        <v>110</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="F67" s="7">
-        <v>26.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="10">
-        <v>292475</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="13">
+      <c r="A68" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="3">
+        <v>272192</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="7">
         <v>32.99</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C69" s="3">
-        <v>219359</v>
+        <v>298620</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="7">
-        <v>4.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="10">
-        <v>294469</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="13">
-        <v>9.99</v>
+      <c r="A70" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="3">
+        <v>258194</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="7">
+        <v>28.99</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C71" s="3">
-        <v>181531</v>
+        <v>258212</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="7">
-        <v>29.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C72" s="3">
-        <v>260461</v>
+        <v>292475</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="7">
-        <v>29.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C73" s="3">
-        <v>303106</v>
+        <v>219359</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="7">
-        <v>56.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C74" s="3">
-        <v>264159</v>
+        <v>294469</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="7">
-        <v>28.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="10">
-        <v>254011</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="13">
-        <v>7.99</v>
+      <c r="A75" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="3">
+        <v>232305</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="7">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C76" s="3">
-        <v>288809</v>
+        <v>181531</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="7">
-        <v>23.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C77" s="3">
-        <v>181505</v>
+        <v>308471</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="7">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="10">
-        <v>246389</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="13">
-        <v>16.989999999999998</v>
+      <c r="A78" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C78" s="3">
+        <v>260461</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="7">
+        <v>29.99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C79" s="10">
-        <v>315120</v>
-      </c>
-      <c r="D79" s="11" t="s">
+      <c r="A79" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="13">
-        <v>29.99</v>
+      <c r="C79" s="3">
+        <v>284802</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="3">
+        <v>303106</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="7">
+        <v>56.99</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C81" s="3">
-        <v>330235</v>
+        <v>264159</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="7">
-        <v>11.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C82" s="3">
-        <v>102127</v>
+        <v>254011</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="7">
-        <v>8.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C83" s="3">
-        <v>223758</v>
+        <v>288809</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="7">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" s="3">
+        <v>297568</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E84" s="5"/>
+      <c r="F84" s="7">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C85" s="3">
+        <v>312531</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="5"/>
+      <c r="F85" s="7">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86" s="3">
+        <v>281680</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E86" s="5"/>
+      <c r="F86" s="7">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C87" s="3">
+        <v>181505</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E87" s="5"/>
+      <c r="F87" s="7">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C88" s="3">
+        <v>246389</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" s="5"/>
+      <c r="F88" s="7">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C89" s="3">
+        <v>315120</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" s="5"/>
+      <c r="F89" s="7">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C90" s="3">
+        <v>315320</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E90" s="5"/>
+      <c r="F90" s="7">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" s="3">
+        <v>114072</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" s="5"/>
+      <c r="F91" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="3">
+        <v>330235</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="7">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C94" s="3">
+        <v>102127</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E94" s="5"/>
+      <c r="F94" s="7">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C95" s="3">
+        <v>223758</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E95" s="5"/>
+      <c r="F95" s="7">
         <v>5.19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - REBAIXA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D87A785-6143-4DFA-A8A5-F3D32BEAB268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF91E0F-197F-46B0-8F06-EB6F09C3C8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
+  </si>
+  <si>
+    <t>LEITE LONGA VIDA ITALAC UHT A2 1L SEMIDESNATADO</t>
   </si>
   <si>
     <t>LEITE LONGA VIDA PIRACANJUBA ZERO LACTOSE 1L DESNATADO</t>
@@ -129,9 +132,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,36 +147,49 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,6 +200,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -214,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -228,11 +250,36 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,15 +583,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="75.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -560,10 +607,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -580,8 +627,8 @@
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6">
+      <c r="E2" s="13"/>
+      <c r="F2" s="9">
         <v>22.99</v>
       </c>
     </row>
@@ -598,8 +645,8 @@
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6">
+      <c r="E3" s="13"/>
+      <c r="F3" s="9">
         <v>18.59</v>
       </c>
     </row>
@@ -616,8 +663,8 @@
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6">
+      <c r="E4" s="13"/>
+      <c r="F4" s="9">
         <v>22.99</v>
       </c>
     </row>
@@ -634,8 +681,8 @@
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6">
+      <c r="E5" s="13"/>
+      <c r="F5" s="9">
         <v>15.99</v>
       </c>
     </row>
@@ -652,12 +699,12 @@
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6">
+      <c r="E7" s="13"/>
+      <c r="F7" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -670,10 +717,10 @@
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="9">
         <v>15.99</v>
       </c>
     </row>
@@ -690,8 +737,8 @@
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6">
+      <c r="E9" s="13"/>
+      <c r="F9" s="9">
         <v>17.59</v>
       </c>
     </row>
@@ -708,10 +755,10 @@
       <c r="D10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -728,12 +775,12 @@
       <c r="D11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6">
+      <c r="E11" s="13"/>
+      <c r="F11" s="9">
         <v>17.59</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -746,10 +793,10 @@
       <c r="D12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="9">
         <v>22.99</v>
       </c>
     </row>
@@ -766,8 +813,8 @@
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6">
+      <c r="E13" s="13"/>
+      <c r="F13" s="9">
         <v>15.59</v>
       </c>
     </row>
@@ -784,8 +831,8 @@
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6">
+      <c r="E14" s="13"/>
+      <c r="F14" s="9">
         <v>28.99</v>
       </c>
     </row>
@@ -802,26 +849,26 @@
       <c r="D15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6">
+      <c r="E15" s="13"/>
+      <c r="F15" s="9">
         <v>31.99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="3">
-        <v>269164</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="6">
+        <v>297027</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6">
+      <c r="E16" s="15"/>
+      <c r="F16" s="11">
         <v>6.99</v>
       </c>
     </row>
@@ -833,32 +880,32 @@
         <v>24</v>
       </c>
       <c r="C17" s="3">
-        <v>328879</v>
+        <v>269164</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6">
+      <c r="E17" s="13"/>
+      <c r="F17" s="9">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3">
+        <v>328879</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="9">
         <v>8.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="3">
-        <v>336165</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6">
-        <v>8.19</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -866,35 +913,17 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3">
+        <v>336165</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
-        <v>329704</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="3">
-        <v>329696</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6">
-        <v>27.99</v>
+      <c r="E21" s="13"/>
+      <c r="F21" s="9">
+        <v>8.19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -902,17 +931,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3">
-        <v>343563</v>
+        <v>329704</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6">
-        <v>31.99</v>
+        <v>31</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="9">
+        <v>25.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,16 +949,52 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3">
+        <v>329696</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="9">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="3">
+        <v>343563</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="9">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="3">
         <v>343562</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6">
+      <c r="D26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="9">
         <v>38.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88829D0-F027-40E4-AD3B-B2F3F1E28722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC3B1E0-DF08-4D11-BD18-541628179B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -292,14 +292,8 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -613,12 +607,12 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -634,10 +628,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -654,8 +648,8 @@
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="9">
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
@@ -672,12 +666,12 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="9">
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -690,10 +684,10 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -710,8 +704,8 @@
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="9">
+      <c r="E5" s="5"/>
+      <c r="F5" s="7">
         <v>3.29</v>
       </c>
     </row>
@@ -728,8 +722,8 @@
       <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="9">
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
         <v>10.99</v>
       </c>
     </row>
@@ -746,8 +740,8 @@
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="9">
+      <c r="E7" s="5"/>
+      <c r="F7" s="7">
         <v>8.49</v>
       </c>
     </row>
@@ -764,8 +758,8 @@
       <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="9">
+      <c r="E8" s="5"/>
+      <c r="F8" s="7">
         <v>4.99</v>
       </c>
     </row>
@@ -782,8 +776,8 @@
       <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="9">
+      <c r="E10" s="5"/>
+      <c r="F10" s="7">
         <v>110.99</v>
       </c>
     </row>
@@ -800,8 +794,8 @@
       <c r="D11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="9">
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
         <v>110.99</v>
       </c>
     </row>
@@ -818,9 +812,9 @@
       <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="9">
-        <v>8.99</v>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>7.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -836,8 +830,8 @@
       <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="9">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
         <v>95.99</v>
       </c>
     </row>
@@ -854,8 +848,8 @@
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="9">
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
         <v>4.6900000000000004</v>
       </c>
     </row>
@@ -872,8 +866,8 @@
       <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9">
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
         <v>36.99</v>
       </c>
     </row>
@@ -890,8 +884,8 @@
       <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="9">
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
         <v>25.99</v>
       </c>
     </row>
@@ -908,8 +902,8 @@
       <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="9">
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
         <v>12.99</v>
       </c>
     </row>
@@ -926,8 +920,8 @@
       <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="9">
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
         <v>11.99</v>
       </c>
     </row>
@@ -944,8 +938,8 @@
       <c r="D20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="9">
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
         <v>22.99</v>
       </c>
     </row>
@@ -962,8 +956,8 @@
       <c r="D21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="9">
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
         <v>70.989999999999995</v>
       </c>
     </row>
@@ -980,8 +974,8 @@
       <c r="D22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="9">
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
         <v>75.989999999999995</v>
       </c>
     </row>
@@ -998,8 +992,8 @@
       <c r="D23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="9">
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
         <v>24.99</v>
       </c>
     </row>
@@ -1016,8 +1010,8 @@
       <c r="D24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="9">
+      <c r="E24" s="5"/>
+      <c r="F24" s="7">
         <v>11.99</v>
       </c>
     </row>
@@ -1034,8 +1028,8 @@
       <c r="D25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="9">
+      <c r="E25" s="5"/>
+      <c r="F25" s="7">
         <v>46.99</v>
       </c>
     </row>
@@ -1052,12 +1046,12 @@
       <c r="D26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="9">
+      <c r="E26" s="5"/>
+      <c r="F26" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -1070,14 +1064,14 @@
       <c r="D27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
@@ -1090,10 +1084,10 @@
       <c r="D28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="7">
         <v>10.99</v>
       </c>
     </row>
@@ -1110,8 +1104,8 @@
       <c r="D29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="9">
+      <c r="E29" s="5"/>
+      <c r="F29" s="7">
         <v>9.99</v>
       </c>
     </row>
@@ -1128,8 +1122,8 @@
       <c r="D30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="9">
+      <c r="E30" s="5"/>
+      <c r="F30" s="7">
         <v>8.99</v>
       </c>
     </row>
@@ -1146,8 +1140,8 @@
       <c r="D31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="9">
+      <c r="E31" s="5"/>
+      <c r="F31" s="7">
         <v>15.89</v>
       </c>
     </row>
@@ -1164,8 +1158,8 @@
       <c r="D32" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="9">
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
         <v>14.99</v>
       </c>
     </row>
@@ -1182,8 +1176,8 @@
       <c r="D33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="9">
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
         <v>8.49</v>
       </c>
     </row>
@@ -1200,8 +1194,8 @@
       <c r="D34" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="9">
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
         <v>25.99</v>
       </c>
     </row>
@@ -1218,8 +1212,8 @@
       <c r="D35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="9">
+      <c r="E35" s="5"/>
+      <c r="F35" s="7">
         <v>15.99</v>
       </c>
     </row>
@@ -1236,8 +1230,8 @@
       <c r="D36" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="9">
+      <c r="E36" s="5"/>
+      <c r="F36" s="7">
         <v>30.99</v>
       </c>
     </row>
@@ -1254,8 +1248,8 @@
       <c r="D37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="9">
+      <c r="E37" s="5"/>
+      <c r="F37" s="7">
         <v>15.89</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9747D5C1-2FE4-4074-8139-65ABDE72C365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D0751-85E9-4C35-9E4F-A4BFE512CB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25890" yWindow="1980" windowWidth="16200" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -52,12 +52,21 @@
     <t>TAPIOCA GOMAC 130G</t>
   </si>
   <si>
+    <t>COCO E GOIABADA, COCO E LEITE CONDENSADO</t>
+  </si>
+  <si>
     <t>TAPIOCA GOMAC 150G</t>
   </si>
   <si>
+    <t>AMENDOIM E GOIABADA CROCANTE, COCO E BANANADA CROCANTE</t>
+  </si>
+  <si>
     <t>TAPIOCA GOMAC 230G</t>
   </si>
   <si>
+    <t>COCO E GOIABADA, COCO E LEITE CONDENSADO, COCO QUEIMADO, ZERO AÇUCAR COCO QUEIMADO</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - CEREAIS MATINAIS</t>
   </si>
   <si>
@@ -121,33 +130,21 @@
     <t xml:space="preserve">MACARRÃO CRISTAL ESPAGUETE 500G INTEGRAL </t>
   </si>
   <si>
-    <t>MACARRÃO ITA DE CECCO 500G FUSILLI CORTI BUCATI</t>
-  </si>
-  <si>
     <t>#02 MERCEARIA - PASTAS E CREMES</t>
   </si>
   <si>
-    <t>PASTA DE AMENDOIM LA GANEXA 450G</t>
-  </si>
-  <si>
-    <t>CHOCOLATE BRANCO, CHOCOLATE CROCANTE, DOCE DE LEITE</t>
-  </si>
-  <si>
     <t>PASTA DE AMENDOIM LA GANEXA 450G CARAMELO E FLOR SAL</t>
   </si>
   <si>
+    <t>PASTA DE AMENDOIM LA GANEXA 450G CHOCOLATE CROCANTE</t>
+  </si>
+  <si>
     <t>PASTA DE AMENDOIM LA GANEXA 450G COOKIES CREAM</t>
   </si>
   <si>
     <t>PASTA DE AMENDOIM LA GANEXA 450G PISTACHE</t>
   </si>
   <si>
-    <t>#02 MERCEARIA - VEGANOS</t>
-  </si>
-  <si>
-    <t>BEBIDA POSSIBLE 1L SABOR ORIGINAL</t>
-  </si>
-  <si>
     <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
   </si>
   <si>
-    <t>BEBIDA MISTA BEATS 269ML GIN E FRUTAS TROPICAIS</t>
-  </si>
-  <si>
     <t>REFRIGERANTE GUARANA ANTARCTICA ZERO PET 200ML</t>
   </si>
   <si>
@@ -181,6 +175,36 @@
     <t xml:space="preserve">CERVEJA ITAIPAVA LONG NECK 250ML </t>
   </si>
   <si>
+    <t>#07 HIGIENE PESSOAL - CABELOS</t>
+  </si>
+  <si>
+    <t>CREME LOREAL ELSEVE NOTURNO 200G CACHOS SONHOS ANTI-TRAVESSEIRO</t>
+  </si>
+  <si>
+    <t>MÁSCARA CAPILAR CHIKAS 700G</t>
+  </si>
+  <si>
+    <t>ACORDA CACHOS ARIBA, CRESPO PODEROSO</t>
+  </si>
+  <si>
+    <t>TINTURA CAPILAR BIOCOLOR MINI KIT 1UN 5.3 CASTANHA CLARO DOURADO</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - DESODORANTE</t>
+  </si>
+  <si>
+    <t>DESODORANTE GB MEN ROLL-ON 50ML 72H SPORT SEM PERFUME</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - ESMALTES</t>
+  </si>
+  <si>
+    <t>ESMALTE RISQUE 8ML</t>
+  </si>
+  <si>
+    <t>A ARTISTA SOU EU, FICA, VAI TER ARCO IRIS, MAR DE POSSIBILIDADES, SERUM HIDRATANTE, VIVENDO DA MINHA ARTE</t>
+  </si>
+  <si>
     <t>#07 HIGIENE PESSOAL - HIGIENE</t>
   </si>
   <si>
@@ -188,6 +212,33 @@
   </si>
   <si>
     <t>HASTES FLEXIVEIS COTTONBABY POTE PROMOCIONAL 150UN</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
+  </si>
+  <si>
+    <t>ANTISSEPTICO BUCAL CEPACOL 250ML</t>
+  </si>
+  <si>
+    <t>CITRUS, MENTA ICE</t>
+  </si>
+  <si>
+    <t>CREME DENTAL ORAL B 70G ANTI CARIES</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - INTIMA</t>
+  </si>
+  <si>
+    <t>CREME HIDRATANTE MONANGE 400ML PELE EXTRA SECA</t>
+  </si>
+  <si>
+    <t>CREME HIDRATANTE MONANGE 50G OLEO DE ABACATE</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - SABONETE</t>
+  </si>
+  <si>
+    <t>SABONETE LIQUIDO INFANTIL TURMA DA XUXINHA 400ML SONO TRANQUILO</t>
   </si>
 </sst>
 </file>
@@ -607,17 +658,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" style="7" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -690,7 +738,9 @@
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="F4" s="9">
         <v>8.99</v>
       </c>
@@ -706,14 +756,16 @@
         <v>342790</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="F5" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -724,9 +776,11 @@
         <v>342792</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="F6" s="9">
         <v>12.99</v>
       </c>
@@ -736,13 +790,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3">
         <v>339456</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="9">
@@ -754,13 +808,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
         <v>339483</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="9">
@@ -772,13 +826,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>185461</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="9">
@@ -790,13 +844,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>100074</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="9">
@@ -808,13 +862,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
         <v>104651</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="9">
@@ -826,13 +880,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3">
         <v>146752</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="9">
@@ -844,13 +898,13 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
         <v>182503</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="9">
@@ -862,13 +916,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3">
         <v>298970</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="9">
@@ -880,13 +934,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3">
         <v>238317</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="9">
@@ -898,13 +952,13 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3">
         <v>228090</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="9">
@@ -916,13 +970,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3">
         <v>328879</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="9">
@@ -934,13 +988,13 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3">
         <v>325485</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="9">
@@ -952,13 +1006,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C19" s="3">
         <v>173725</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="9">
@@ -970,35 +1024,33 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3">
-        <v>319565</v>
+        <v>346333</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="9">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3">
         <v>335885</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>36</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E21" s="6"/>
       <c r="F21" s="9">
         <v>22.99</v>
       </c>
@@ -1008,17 +1060,17 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3">
-        <v>346333</v>
+        <v>335897</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="9">
-        <v>33.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,34 +1078,16 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3">
-        <v>335897</v>
+        <v>335893</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="9">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="3">
-        <v>335893</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="9">
         <v>33.9</v>
       </c>
     </row>
@@ -1062,17 +1096,17 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3">
-        <v>267427</v>
+        <v>117826</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="9">
-        <v>9.99</v>
+        <v>95.99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1080,17 +1114,35 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3">
-        <v>117826</v>
+        <v>275857</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="9">
-        <v>95.99</v>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="3">
+        <v>286959</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,17 +1150,17 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C29" s="3">
-        <v>302070</v>
+        <v>198516</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="9">
-        <v>6.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,35 +1168,17 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3">
-        <v>275857</v>
+        <v>117413</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="9">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="3">
-        <v>286959</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="9">
-        <v>12.99</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,17 +1186,17 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C32" s="3">
-        <v>198516</v>
+        <v>265622</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="9">
-        <v>2.39</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1173,14 +1207,34 @@
         <v>51</v>
       </c>
       <c r="C33" s="3">
-        <v>117413</v>
+        <v>311070</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="F33" s="9">
-        <v>4.29</v>
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="3">
+        <v>308254</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1188,39 +1242,168 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3">
-        <v>256740</v>
+        <v>308784</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="9">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="3">
+        <v>162175</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="3">
+        <v>256740</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="3">
         <v>182485</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="9">
+      <c r="D38" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="9">
         <v>8.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="3">
+        <v>297554</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="9">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="3">
+        <v>170506</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="9">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="3">
+        <v>303529</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="9">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="3">
+        <v>293647</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="9">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="3">
+        <v>289231</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="9">
+        <v>23.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - REBAIXA.xlsx
+++ b/giro_da_praça_ofertas - REBAIXA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D0751-85E9-4C35-9E4F-A4BFE512CB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C94D0AF-2EE5-4A3D-ACFC-8CB6580A6673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25890" yWindow="1980" windowWidth="16200" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -43,10 +43,16 @@
     <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
   </si>
   <si>
-    <t>BISCOITO CREAM CRACKER FORTALEZA 400G PETIT  SALGADO</t>
-  </si>
-  <si>
-    <t>BISCOITO VITARELLA MARIA 350G CHOCOLATE</t>
+    <t>BISCOITO BUTTER COOKIES DANESITA 340G CLASSIC</t>
+  </si>
+  <si>
+    <t>BISCOITO MAISENA VITARELLA 350G</t>
+  </si>
+  <si>
+    <t>CHOCOLATE, LEITE, TRADICIONAL</t>
+  </si>
+  <si>
+    <t>BISCOITO MARIA VITARELLA 350G</t>
   </si>
   <si>
     <t>TAPIOCA GOMAC 130G</t>
@@ -79,6 +85,9 @@
     <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
   </si>
   <si>
+    <t>BOMBOM NESTLE ALPINO BAG 195G CHOCOLATE</t>
+  </si>
+  <si>
     <t>DOCE DE LEITE ITALAC 350G</t>
   </si>
   <si>
@@ -106,6 +115,12 @@
     <t>BEBIDA LACTEA PIRACANJUBA 1L WHEY COCO</t>
   </si>
   <si>
+    <t>DANONINHO 320G MULTIFRUTAS</t>
+  </si>
+  <si>
+    <t>IOGURTE DANONE 1250G VITAMINA DE FRUTAS</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
   </si>
   <si>
@@ -130,6 +145,12 @@
     <t xml:space="preserve">MACARRÃO CRISTAL ESPAGUETE 500G INTEGRAL </t>
   </si>
   <si>
+    <t>RAVIOLI MEZZANI 400G</t>
+  </si>
+  <si>
+    <t>4 QUEIJOS, FRANGO</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - PASTAS E CREMES</t>
   </si>
   <si>
@@ -139,9 +160,6 @@
     <t>PASTA DE AMENDOIM LA GANEXA 450G CHOCOLATE CROCANTE</t>
   </si>
   <si>
-    <t>PASTA DE AMENDOIM LA GANEXA 450G COOKIES CREAM</t>
-  </si>
-  <si>
     <t>PASTA DE AMENDOIM LA GANEXA 450G PISTACHE</t>
   </si>
   <si>
@@ -202,9 +220,6 @@
     <t>ESMALTE RISQUE 8ML</t>
   </si>
   <si>
-    <t>A ARTISTA SOU EU, FICA, VAI TER ARCO IRIS, MAR DE POSSIBILIDADES, SERUM HIDRATANTE, VIVENDO DA MINHA ARTE</t>
-  </si>
-  <si>
     <t>#07 HIGIENE PESSOAL - HIGIENE</t>
   </si>
   <si>
@@ -223,13 +238,10 @@
     <t>CITRUS, MENTA ICE</t>
   </si>
   <si>
-    <t>CREME DENTAL ORAL B 70G ANTI CARIES</t>
-  </si>
-  <si>
     <t>#07 HIGIENE PESSOAL - INTIMA</t>
   </si>
   <si>
-    <t>CREME HIDRATANTE MONANGE 400ML PELE EXTRA SECA</t>
+    <t>CREME HIDRATANTE MONANGE 400ML Q10 FIRMADOR PELE EXTRA SECA</t>
   </si>
   <si>
     <t>CREME HIDRATANTE MONANGE 50G OLEO DE ABACATE</t>
@@ -326,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -340,14 +352,8 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -356,6 +362,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,15 +665,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -682,10 +689,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -697,14 +704,14 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>101514</v>
+        <v>336144</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="9">
-        <v>10.99</v>
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
+        <v>34.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -715,13 +722,15 @@
         <v>6</v>
       </c>
       <c r="C3" s="3">
-        <v>264678</v>
+        <v>263612</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="9">
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7">
         <v>8.99</v>
       </c>
     </row>
@@ -733,15 +742,15 @@
         <v>6</v>
       </c>
       <c r="C4" s="3">
-        <v>342796</v>
+        <v>264678</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>8.99</v>
       </c>
     </row>
@@ -753,19 +762,19 @@
         <v>6</v>
       </c>
       <c r="C5" s="3">
-        <v>342790</v>
+        <v>342796</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="9">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="F5" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -773,16 +782,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="3">
-        <v>342792</v>
+        <v>342790</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="9">
-        <v>12.99</v>
+      <c r="F6" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,17 +799,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>342792</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
-        <v>339456</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="9">
-        <v>4.99</v>
+      <c r="F7" s="7">
+        <v>12.99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -808,17 +819,17 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3">
-        <v>339483</v>
+        <v>339456</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="9">
-        <v>6.99</v>
+        <v>18</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -826,17 +837,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3">
-        <v>185461</v>
+        <v>339483</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="9">
-        <v>9.99</v>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -847,14 +858,14 @@
         <v>20</v>
       </c>
       <c r="C10" s="3">
-        <v>100074</v>
+        <v>221534</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="9">
-        <v>10.99</v>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7">
+        <v>25.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -862,17 +873,17 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
+        <v>185461</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3">
-        <v>104651</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="9">
-        <v>6.99</v>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
+        <v>9.99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -880,17 +891,17 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3">
-        <v>146752</v>
+        <v>100074</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="9">
-        <v>6.99</v>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -898,17 +909,17 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3">
-        <v>182503</v>
+        <v>104651</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="9">
-        <v>5.49</v>
+        <v>26</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -916,17 +927,17 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3">
-        <v>298970</v>
+        <v>146752</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="9">
-        <v>10.99</v>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -934,17 +945,17 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3">
+        <v>182503</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="3">
-        <v>238317</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="9">
-        <v>9.99</v>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
+        <v>5.49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -952,17 +963,17 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3">
-        <v>228090</v>
+        <v>298970</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9">
-        <v>3.99</v>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,17 +981,17 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3">
-        <v>328879</v>
+        <v>173606</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="9">
-        <v>8.49</v>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -988,16 +999,16 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3">
+        <v>246976</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="3">
-        <v>325485</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="9">
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -1006,17 +1017,17 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3">
+        <v>238317</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3">
-        <v>173725</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="9">
-        <v>4.99</v>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
+        <v>9.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,17 +1035,17 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3">
-        <v>346333</v>
+        <v>228090</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="9">
-        <v>33.99</v>
+        <v>35</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
+        <v>3.99</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,17 +1053,17 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="3">
+        <v>328879</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="3">
-        <v>335885</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="9">
-        <v>22.99</v>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>8.49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1060,17 +1071,17 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3">
-        <v>335897</v>
+        <v>325485</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="9">
-        <v>23.99</v>
+        <v>38</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1078,17 +1089,37 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3">
-        <v>335893</v>
+        <v>173725</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="9">
-        <v>33.9</v>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="3">
+        <v>104812</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,17 +1127,35 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3">
-        <v>117826</v>
+        <v>346333</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="9">
-        <v>95.99</v>
+        <v>44</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="3">
+        <v>335885</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="7">
+        <v>22.99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1117,32 +1166,14 @@
         <v>43</v>
       </c>
       <c r="C27" s="3">
-        <v>275857</v>
+        <v>335893</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="9">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="3">
-        <v>286959</v>
-      </c>
-      <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="9">
-        <v>12.99</v>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
+        <v>33.9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1153,32 +1184,32 @@
         <v>47</v>
       </c>
       <c r="C29" s="3">
-        <v>198516</v>
+        <v>117826</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="9">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="7">
+        <v>95.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="3">
-        <v>117413</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="C31" s="3">
+        <v>275857</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="9">
-        <v>4.29</v>
+      <c r="E31" s="5"/>
+      <c r="F31" s="7">
+        <v>1.69</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,14 +1220,14 @@
         <v>51</v>
       </c>
       <c r="C32" s="3">
-        <v>265622</v>
+        <v>286959</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="9">
-        <v>24.99</v>
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
+        <v>12.99</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,19 +1235,17 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" s="3">
-        <v>311070</v>
+        <v>198516</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F33" s="9">
-        <v>22.99</v>
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
+        <v>2.39</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1224,55 +1253,35 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C34" s="3">
-        <v>308254</v>
+        <v>117413</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="9">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="3">
-        <v>308784</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="9">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="3">
+        <v>265622</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="3">
-        <v>162175</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F36" s="9">
-        <v>4.99</v>
+      <c r="E36" s="5"/>
+      <c r="F36" s="7">
+        <v>24.99</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,17 +1289,19 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C37" s="3">
-        <v>256740</v>
+        <v>311070</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="9">
-        <v>9.99</v>
+        <v>59</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="7">
+        <v>22.99</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1298,17 +1309,17 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="3">
+        <v>308254</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="3">
-        <v>182485</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="9">
-        <v>8.99</v>
+      <c r="E38" s="5"/>
+      <c r="F38" s="7">
+        <v>12.99</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1316,19 +1327,17 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C39" s="3">
-        <v>297554</v>
+        <v>308784</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F39" s="9">
-        <v>10.99</v>
+        <v>63</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="7">
+        <v>7.99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1339,14 +1348,14 @@
         <v>64</v>
       </c>
       <c r="C40" s="3">
-        <v>170506</v>
+        <v>162175</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="9">
-        <v>3.99</v>
+        <v>65</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1354,17 +1363,17 @@
         <v>5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C41" s="3">
-        <v>303529</v>
+        <v>256740</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="9">
-        <v>25.99</v>
+        <v>67</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="7">
+        <v>9.99</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1372,17 +1381,17 @@
         <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="3">
+        <v>182485</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="3">
-        <v>293647</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="9">
-        <v>17.989999999999998</v>
+      <c r="E42" s="5"/>
+      <c r="F42" s="7">
+        <v>8.99</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,16 +1399,72 @@
         <v>5</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="3">
+        <v>297554</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="3">
+      <c r="F43" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="3">
+        <v>303529</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="7">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="3">
+        <v>293647</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="7">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="3">
         <v>289231</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="9">
+      <c r="D46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="7">
         <v>23.99</v>
       </c>
     </row>
